--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="12.5703125" customWidth="1" style="15" min="1" max="1"/>
@@ -799,14 +799,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45163.60929995863</v>
+        <v>45232</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -848,16 +844,6 @@
       <c r="A11" s="23" t="n"/>
       <c r="E11" s="6" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="18" customHeight="1" s="15">
       <c r="A22" s="8" t="inlineStr">
         <is>
@@ -1075,23 +1061,22 @@
       </c>
       <c r="F44" s="11" t="n"/>
     </row>
-    <row r="45"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45232</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -1063,20 +1063,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A9:D9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45238</v>
+        <v>45244</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -1063,20 +1063,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -1063,20 +1063,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A9:D9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -1063,20 +1063,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -799,7 +799,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="12.5703125" customWidth="1" style="15" min="1" max="1"/>
@@ -799,10 +799,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45266</v>
+        <v>45230.5421020037</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -844,6 +848,16 @@
       <c r="A11" s="23" t="n"/>
       <c r="E11" s="6" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="18" customHeight="1" s="15">
       <c r="A22" s="8" t="inlineStr">
         <is>
@@ -875,7 +889,7 @@
       </c>
       <c r="C23" s="20" t="n"/>
       <c r="D23" s="10" t="n">
-        <v>38.294</v>
+        <v>44.03</v>
       </c>
       <c r="F23" s="11" t="n"/>
     </row>
@@ -892,7 +906,7 @@
       </c>
       <c r="C24" s="20" t="n"/>
       <c r="D24" s="10" t="n">
-        <v>38.294</v>
+        <v>44.03</v>
       </c>
       <c r="F24" s="11" t="n"/>
     </row>
@@ -909,7 +923,7 @@
       </c>
       <c r="C25" s="20" t="n"/>
       <c r="D25" s="12" t="n">
-        <v>22.693</v>
+        <v>26.09</v>
       </c>
       <c r="F25" s="11" t="n"/>
     </row>
@@ -926,7 +940,7 @@
       </c>
       <c r="C26" s="18" t="n"/>
       <c r="D26" s="12" t="n">
-        <v>22.693</v>
+        <v>26.09</v>
       </c>
       <c r="F26" s="11" t="n"/>
     </row>
@@ -1006,7 +1020,7 @@
       </c>
       <c r="C41" s="18" t="n"/>
       <c r="D41" s="10" t="n">
-        <v>87.58499999999999</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="F41" s="11" t="n"/>
     </row>
@@ -1023,7 +1037,7 @@
       </c>
       <c r="C42" s="18" t="n"/>
       <c r="D42" s="10" t="n">
-        <v>87.58499999999999</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="F42" s="11" t="n"/>
     </row>
@@ -1040,7 +1054,7 @@
       </c>
       <c r="C43" s="18" t="n"/>
       <c r="D43" s="10" t="n">
-        <v>96.43899999999999</v>
+        <v>110.9</v>
       </c>
       <c r="F43" s="11" t="n"/>
     </row>
@@ -1057,26 +1071,27 @@
       </c>
       <c r="C44" s="18" t="n"/>
       <c r="D44" s="10" t="n">
-        <v>120.652</v>
+        <v>138.75</v>
       </c>
       <c r="F44" s="11" t="n"/>
     </row>
+    <row r="45"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
+++ b/LISTAS/mi/SOPORTE VISILLO y fleje DISMAY.xlsx
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="12.5703125" customWidth="1" style="15" min="1" max="1"/>
@@ -799,14 +799,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="25" t="n">
-        <v>45230.5421020037</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -848,16 +844,6 @@
       <c r="A11" s="23" t="n"/>
       <c r="E11" s="6" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="18" customHeight="1" s="15">
       <c r="A22" s="8" t="inlineStr">
         <is>
@@ -889,7 +875,7 @@
       </c>
       <c r="C23" s="20" t="n"/>
       <c r="D23" s="10" t="n">
-        <v>44.03</v>
+        <v>38.294</v>
       </c>
       <c r="F23" s="11" t="n"/>
     </row>
@@ -906,7 +892,7 @@
       </c>
       <c r="C24" s="20" t="n"/>
       <c r="D24" s="10" t="n">
-        <v>44.03</v>
+        <v>38.294</v>
       </c>
       <c r="F24" s="11" t="n"/>
     </row>
@@ -923,7 +909,7 @@
       </c>
       <c r="C25" s="20" t="n"/>
       <c r="D25" s="12" t="n">
-        <v>26.09</v>
+        <v>22.693</v>
       </c>
       <c r="F25" s="11" t="n"/>
     </row>
@@ -940,7 +926,7 @@
       </c>
       <c r="C26" s="18" t="n"/>
       <c r="D26" s="12" t="n">
-        <v>26.09</v>
+        <v>22.693</v>
       </c>
       <c r="F26" s="11" t="n"/>
     </row>
@@ -1020,7 +1006,7 @@
       </c>
       <c r="C41" s="18" t="n"/>
       <c r="D41" s="10" t="n">
-        <v>97.23999999999999</v>
+        <v>87.58499999999999</v>
       </c>
       <c r="F41" s="11" t="n"/>
     </row>
@@ -1037,7 +1023,7 @@
       </c>
       <c r="C42" s="18" t="n"/>
       <c r="D42" s="10" t="n">
-        <v>97.23999999999999</v>
+        <v>87.58499999999999</v>
       </c>
       <c r="F42" s="11" t="n"/>
     </row>
@@ -1054,7 +1040,7 @@
       </c>
       <c r="C43" s="18" t="n"/>
       <c r="D43" s="10" t="n">
-        <v>110.9</v>
+        <v>96.43899999999999</v>
       </c>
       <c r="F43" s="11" t="n"/>
     </row>
@@ -1071,27 +1057,26 @@
       </c>
       <c r="C44" s="18" t="n"/>
       <c r="D44" s="10" t="n">
-        <v>138.75</v>
+        <v>120.652</v>
       </c>
       <c r="F44" s="11" t="n"/>
     </row>
-    <row r="45"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
